--- a/data/trans_camb/P42C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P42C_R-Habitat-trans_camb.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -506,8 +506,6 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,22 +517,16 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -555,16 +547,6 @@
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2012</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2023/2012</t>
         </is>
@@ -577,8 +559,6 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -593,12 +573,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7,31</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4,19</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -607,16 +587,6 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,31</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-4,19</t>
         </is>
@@ -631,32 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,61; -3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,01; 0,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -2,88</t>
+          <t>-11,61; -3,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 0,16</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-11,78; -2,88</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-8,5; 0,16</t>
+          <t>-9,01; 0,21</t>
         </is>
       </c>
     </row>
@@ -669,12 +629,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-42,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-24,45%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -683,16 +643,6 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-24,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-42,65%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-24,45%</t>
         </is>
@@ -707,32 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,0; -19,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-45,69; 1,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,9; -17,95</t>
+          <t>-59,0; -19,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 2,3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-59,9; -17,95</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-43,6; 2,3</t>
+          <t>-45,69; 1,61</t>
         </is>
       </c>
     </row>
@@ -749,12 +689,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13,79</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6,53</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -763,16 +703,6 @@
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-6,53</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-13,79</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-6,53</t>
         </is>
@@ -787,32 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,83; -9,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,26; -2,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -9,28</t>
+          <t>-17,83; -9,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,94; -1,96</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-18,01; -9,28</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-10,94; -1,96</t>
+          <t>-11,26; -2,09</t>
         </is>
       </c>
     </row>
@@ -825,12 +745,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-49,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-23,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -839,16 +759,6 @@
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-23,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-49,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-23,6%</t>
         </is>
@@ -863,32 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,72; -37,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,69; -8,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,44; -36,91</t>
+          <t>-59,72; -37,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,44; -7,77</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-59,44; -36,91</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-36,44; -7,77</t>
+          <t>-37,69; -8,16</t>
         </is>
       </c>
     </row>
@@ -905,12 +805,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9,07</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -919,16 +819,6 @@
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,76</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-9,07</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,76</t>
         </is>
@@ -943,32 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,64; -4,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,0; 11,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -4,47</t>
+          <t>-13,64; -4,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 11,78</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-14,39; -4,47</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 11,78</t>
+          <t>-2,0; 11,54</t>
         </is>
       </c>
     </row>
@@ -981,12 +861,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-35,96%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -995,16 +875,6 @@
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-35,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>22,83%</t>
         </is>
@@ -1019,32 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-49,69; -18,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,53; 49,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,33; -18,83</t>
+          <t>-49,69; -18,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 50,28</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-50,33; -18,83</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-6,8; 50,28</t>
+          <t>-6,53; 49,8</t>
         </is>
       </c>
     </row>
@@ -1061,12 +921,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,78</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1075,16 +935,6 @@
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,78</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,73</t>
         </is>
@@ -1099,32 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,73; 0,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,84; 6,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 0,22</t>
+          <t>-7,73; 0,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 7,11</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-7,72; 0,22</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-6,45; 7,11</t>
+          <t>-6,84; 6,56</t>
         </is>
       </c>
     </row>
@@ -1137,12 +977,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-15,97%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1151,16 +991,6 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-15,97%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>7,3%</t>
         </is>
@@ -1175,32 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,61; 0,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-26,33; 29,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 1,17</t>
+          <t>-30,61; 0,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 32,12</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-29,96; 1,17</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-26,07; 32,12</t>
+          <t>-26,33; 29,11</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1037,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8,46</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1231,16 +1051,6 @@
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-8,46</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-0,73</t>
         </is>
@@ -1255,32 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,67; -6,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,14; 1,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -6,45</t>
+          <t>-10,67; -6,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,74</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-10,63; -6,45</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; 1,74</t>
+          <t>-4,14; 1,83</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1093,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-35,36%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,07%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1307,16 +1107,6 @@
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-3,07%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-35,36%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-3,07%</t>
         </is>
@@ -1331,32 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-43,0; -27,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,57; 8,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,15; -28,23</t>
+          <t>-43,0; -27,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 7,53</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-42,15; -28,23</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-16,22; 7,53</t>
+          <t>-16,57; 8,07</t>
         </is>
       </c>
     </row>
@@ -1368,11 +1148,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A20:A23"/>

--- a/data/trans_camb/P42C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P42C_R-Habitat-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-4,19</t>
+          <t>-4,27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,19</t>
+          <t>-4,27</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -3,17</t>
+          <t>-12,13; -3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 0,21</t>
+          <t>-8,64; 0,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -3,17</t>
+          <t>-12,13; -3,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 0,21</t>
+          <t>-8,64; 0,41</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-24,45%</t>
+          <t>-24,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-24,45%</t>
+          <t>-24,93%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,0; -19,6</t>
+          <t>-60,25; -20,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,69; 1,61</t>
+          <t>-44,39; 2,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,0; -19,6</t>
+          <t>-60,25; -20,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,69; 1,61</t>
+          <t>-44,39; 2,99</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-6,53</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,53</t>
+          <t>-6,17</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,83; -9,44</t>
+          <t>-18,23; -9,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -2,09</t>
+          <t>-11,2; -1,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,83; -9,44</t>
+          <t>-18,23; -9,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -2,09</t>
+          <t>-11,2; -1,71</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-23,6%</t>
+          <t>-22,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-23,6%</t>
+          <t>-22,32%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,72; -37,27</t>
+          <t>-60,06; -38,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,69; -8,16</t>
+          <t>-36,67; -6,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,72; -37,27</t>
+          <t>-60,06; -38,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,69; -8,16</t>
+          <t>-36,67; -6,74</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>6,71</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>6,71</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; -4,22</t>
+          <t>-14,03; -4,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 11,54</t>
+          <t>1,22; 11,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; -4,22</t>
+          <t>-14,03; -4,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 11,54</t>
+          <t>1,22; 11,85</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,69; -18,78</t>
+          <t>-50,03; -19,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 49,8</t>
+          <t>4,36; 53,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,69; -18,78</t>
+          <t>-50,03; -19,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 49,8</t>
+          <t>4,36; 53,18</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>4,65</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,13</t>
+          <t>-7,79; 0,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 6,56</t>
+          <t>0,61; 9,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,13</t>
+          <t>-7,79; 0,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 6,56</t>
+          <t>0,61; 9,44</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 0,45</t>
+          <t>-30,16; 3,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 29,11</t>
+          <t>2,43; 44,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 0,45</t>
+          <t>-30,16; 3,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 29,11</t>
+          <t>2,43; 44,39</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -6,35</t>
+          <t>-10,67; -6,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,83</t>
+          <t>-2,14; 2,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -6,35</t>
+          <t>-10,67; -6,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,83</t>
+          <t>-2,14; 2,75</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-3,07%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-3,07%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,0; -27,99</t>
+          <t>-42,36; -27,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 8,07</t>
+          <t>-8,57; 12,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,0; -27,99</t>
+          <t>-42,36; -27,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 8,07</t>
+          <t>-8,57; 12,2</t>
         </is>
       </c>
     </row>
